--- a/www/download/COUNTRY.HUN.rpO1.xlsx
+++ b/www/download/COUNTRY.HUN.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Hungria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>124.999994757928</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>152.439020974766</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>186.219741832314</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>214.132754361592</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>236.966824914034</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>280.898870389336</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>286.532947285858</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>257.069406991601</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>224.215247886593</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>202.429153668107</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>199.203185952529</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>210.08403650247</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>183.486236851735</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170.356886305572</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200.723810528585</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.025</t>
+          <t>1.65287044685492</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>1.55476026712863</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.026</t>
+          <t>1.4799651880011</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.097</t>
+          <t>1.48108613999926</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.208</t>
+          <t>1.56765866610663</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>1.48220546522422</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.232</t>
+          <t>1.4567472556591</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.224</t>
+          <t>1.53229938974592</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.227</t>
+          <t>1.99963687384369</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.166</t>
+          <t>1.60126248061924</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.156</t>
+          <t>1.63095185516947</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.182</t>
+          <t>1.58891955247287</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.169</t>
+          <t>1.53776305733821</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.069</t>
+          <t>1.47219521845478</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3.958</t>
+          <t>1.41940378669085</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.334</t>
+          <t>4.01696635687475</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.299</t>
+          <t>3.87746768910378</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.304</t>
+          <t>3.7572145094885</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.402</t>
+          <t>3.74398434597606</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.478</t>
+          <t>4.02939747132105</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.562</t>
+          <t>3.90898402534954</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.589</t>
+          <t>3.76633181949022</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.598</t>
+          <t>3.86943248036802</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.647</t>
+          <t>4.21309095672831</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3.599</t>
+          <t>4.00695917749684</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.627</t>
+          <t>4.07373582204678</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.674</t>
+          <t>3.99003308761369</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.683</t>
+          <t>3.91579146739299</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.647</t>
+          <t>3.84521692045796</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.561</t>
+          <t>3.79000549486575</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8079.711</t>
+          <t>5.29737851537361</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8069.551</t>
+          <t>5.11652018230601</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8160.662</t>
+          <t>4.96250160541812</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8290.864</t>
+          <t>4.95018120659266</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8587.375</t>
+          <t>5.3872863359848</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8673.529</t>
+          <t>5.14307582314013</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8452.565</t>
+          <t>4.92543703317205</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>8474.813</t>
+          <t>4.96731165464197</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8369.327</t>
+          <t>2.94432608057651</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>8304.772</t>
+          <t>5.19957326623537</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>8284.195</t>
+          <t>5.31613823159505</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>8317.391</t>
+          <t>5.22440616337318</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>8277.404</t>
+          <t>4.95378996226389</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>8076.164</t>
+          <t>5.16745445393949</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7854.807</t>
+          <t>5.15294595454545</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6653.528</t>
+          <t>2778749986139.68</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6558.125</t>
+          <t>2458663897956.22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6659.477</t>
+          <t>2574704105514.69</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6856.273</t>
+          <t>2917386067559.87</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7066.93</t>
+          <t>3193301745050.09</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6961.417</t>
+          <t>3681081128453.42</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7127.012</t>
+          <t>4143364003437.79</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7176.956</t>
+          <t>4630949826326.04</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7159.213</t>
+          <t>5392239479830.84</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>7123.6</t>
+          <t>5331722703574.77</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7199.949</t>
+          <t>5164430121970.11</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7275.75</t>
+          <t>4547536920938.16</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7282.681</t>
+          <t>4008345454260.29</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7217.871</t>
+          <t>3032180261923.04</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6982.465</t>
+          <t>2269275882668.18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>379458372850.234</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>334891351537.447</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>345330765632.111</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>392164265755.013</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>411009230322.065</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>462268534346.667</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>563765663936.097</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>689566245926.727</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>835698626781.881</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>837424293929.774</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>816872419243.828</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>707151139532.558</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>648678500176.205</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>545942373490.476</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>33.11</t>
+          <t>433244136391.035</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>1087098282.6877</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>946847059.038448</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>964118372.43496</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.39</t>
+          <t>1044722154.95497</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>61.57</t>
+          <t>1119653535.75412</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>60.67</t>
+          <t>1275961007.39201</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>61.15</t>
+          <t>1308961573.06298</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>61.57</t>
+          <t>1249679226.88214</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>58.22</t>
+          <t>1180469335.88555</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>967297272.582128</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>863648020.137043</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>708378981.039004</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>59.38</t>
+          <t>520183650.925933</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>57.96</t>
+          <t>343562593.744234</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>331940409.691571</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>54960.603266705</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>54003.5583466529</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>55061.2700141252</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>55942.0706475024</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>55490.7260263588</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12.91</t>
+          <t>56709.0671654374</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>61874.8058691657</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>76967.8464588136</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>96576.3897106105</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>117142.052283923</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>126606.367393054</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>124953.267722249</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>149098.73685307</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>163585.227672021</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>132706.557912192</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>124923.380918441</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>124152.040610457</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>127280.384590126</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>130881.795896725</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>133539.096807122</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>135731.479216264</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>144464.190735084</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>13.84</t>
+          <t>168815.498058795</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>206537.013520092</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>245454.135111542</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>16.59</t>
+          <t>266135.815712359</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>271835.459488522</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>319532.412795949</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>322041.323674551</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>250923.703524406</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>68.12</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>68.36</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>68.27</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>68.93</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>67.54</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>24304.5814167978</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>23651.167794313</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>21725.0215732598</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>20648.6634398311</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15.82</t>
+          <t>20052.6737212134</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>17200.1115339258</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17030.5062153724</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>19352.8263208026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>23410.4365570017</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>27383.1279901209</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>28516.1745862453</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>14.37</t>
+          <t>28261.7747013932</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>13.97</t>
+          <t>33488.6332777695</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>124.999994757928</t>
+          <t>113821.71340125</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>152.439020974766</t>
+          <t>101519.389988046</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>186.219741832314</t>
+          <t>104517.699880876</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>214.132754361592</t>
+          <t>115282.043657429</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>236.966824914034</t>
+          <t>118171.230673131</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>280.898870389336</t>
+          <t>129765.015953416</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>286.532947285858</t>
+          <t>157067.146515713</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>257.069406991601</t>
+          <t>191651.587797379</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>224.215247886593</t>
+          <t>229135.998424501</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>202.429153668107</t>
+          <t>232659.091786204</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>199.203185952529</t>
+          <t>225200.173914722</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>210.08403650247</t>
+          <t>192500.598075938</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>183.486236851735</t>
+          <t>176129.996819456</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>170.356886305572</t>
+          <t>149714.107324665</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>200.723810528585</t>
+          <t>121674.242370237</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-70619686990.5856</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>-36588166593.4321</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>4008948079.10752</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>28031725453.9965</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>55913109108.7937</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>66933801338.6903</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>122125636526.373</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>162392744116.726</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>203559769707.135</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>204877859632.701</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>216203257920.329</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>254092419308.234</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>195345720423.113</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>217799670221.633</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>195780210456.459</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-79533016307.7222</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-46397517962.1186</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>-4352919551.50508</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>29703246146.697</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>59452205014.9792</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>42744632528.6435</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>60281153074.4287</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>75790215575.9923</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>157283231123.44</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>160273718792.261</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>138736164501.62</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>165264342664.803</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>122661277752.6</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>161290562072.04</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>148604499967.252</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>8913329317.13663</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>9809351368.68649</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>8361867630.61259</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>-1671520692.70056</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>-3539095906.18553</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>24189168810.0467</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>61844483451.9448</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>86602528540.7337</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>46276538583.695</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>44604140840.44</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>77467093418.7096</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>88828076643.4307</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>72684442670.5124</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56509108149.5937</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47175710489.2071</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>510203.285156047</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>441556.847332049</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>442870.592138279</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>485852.509467777</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>513705.68184924</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>553052.805465902</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>651395.031267353</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>806111.866664428</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>990795.492145023</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>976870.548801521</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>951960.105735084</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>797445.402590339</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>713414.411976592</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>591334.041891596</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>470469.456128696</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>505435.207355835</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>453360.896473694</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>479788.132874124</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>538616.468029672</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>560622.815157025</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>658212.443940183</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>772031.213191917</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>942755.448243727</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1143173.30235009</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>1181239.3233659</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>1152934.27076811</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>993478.114370062</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>915065.191382312</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>794029.378113683</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>653103.140380467</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>165.29</t>
+          <t>16317.3023958859</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>155.48</t>
+          <t>17439.8262165984</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>20632.6046639379</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>148.11</t>
+          <t>24583.8072247669</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>156.77</t>
+          <t>26340.2537911258</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>148.22</t>
+          <t>30283.0713820076</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>145.67</t>
+          <t>33065.2271460219</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>153.23</t>
+          <t>37475.6458533138</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>199.96</t>
+          <t>46029.4366018815</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>160.13</t>
+          <t>59362.4107947105</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>163.1</t>
+          <t>67510.2395437571</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>158.89</t>
+          <t>81417.6298164548</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>153.78</t>
+          <t>103086.968022661</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>147.22</t>
+          <t>116244.717550639</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>141.94</t>
+          <t>86121.6412323762</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>401.7</t>
+          <t>549790577391.74</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>387.75</t>
+          <t>498001103311.352</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>375.72</t>
+          <t>599382261551.917</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>374.4</t>
+          <t>788482912104.208</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>402.94</t>
+          <t>897896895741.291</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>390.9</t>
+          <t>1186979951868.99</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>376.63</t>
+          <t>1334443781788.85</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>386.94</t>
+          <t>1431460737300.53</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>421.31</t>
+          <t>1650811623213.2</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>400.7</t>
+          <t>1789120938744.46</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>407.37</t>
+          <t>1782518461705.74</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1769038293155.55</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>391.58</t>
+          <t>1662360146561.76</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>384.52</t>
+          <t>1287753049254.08</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>906545329926.255</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>529.74</t>
+          <t>18351.7452046612</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>511.65</t>
+          <t>19801.5743993344</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>496.25</t>
+          <t>22427.2604938212</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>495.02</t>
+          <t>27128.315091272</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>538.73</t>
+          <t>29157.66171935</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>514.31</t>
+          <t>33386.6581357788</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>492.54</t>
+          <t>35449.8129193804</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>496.73</t>
+          <t>39852.588833931</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>294.43</t>
+          <t>50094.7183786812</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>519.96</t>
+          <t>63431.1063138496</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>531.61</t>
+          <t>70392.2969058567</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>522.44</t>
+          <t>83013.0779519612</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>495.38</t>
+          <t>101586.191481021</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>516.75</t>
+          <t>116238.965556102</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>515.29</t>
+          <t>81386.0289612402</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2034609.715</t>
+          <t>553421835690.433</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1827089.296</t>
+          <t>538275545974.805</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1931779.596</t>
+          <t>663217207912.14</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2206594.251</t>
+          <t>911937003974.737</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2359332.904</t>
+          <t>1067569037669.72</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2797644.451</t>
+          <t>1395137630812.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3266956.619</t>
+          <t>1573253205900.91</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3981909.587</t>
+          <t>1705986319109.93</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4831895.181</t>
+          <t>2035018575342.09</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4921050.109</t>
+          <t>2142300744938.09</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>4791441.489</t>
+          <t>2092111361333.1</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>4154325.103</t>
+          <t>2067206580185.53</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3814945.216</t>
+          <t>1827179177641.01</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3230660.555</t>
+          <t>1505466240658.92</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2584947.356</t>
+          <t>1032267752815.28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1700913.671</t>
+          <t>-2034.44280877537</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1456604.196</t>
+          <t>-2361.74818273608</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1463262.594</t>
+          <t>-1794.65582988327</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1652763.836</t>
+          <t>-2544.50786650501</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1786710.485</t>
+          <t>-2817.40792822415</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1970168.215</t>
+          <t>-3103.58675377123</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2338071.076</t>
+          <t>-2384.5857733585</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2900406.618</t>
+          <t>-2376.94298061721</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3613602.567</t>
+          <t>-4065.28177679976</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3516110.732</t>
+          <t>-4068.6955191391</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3453061.075</t>
+          <t>-2882.05736209961</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2929416.484</t>
+          <t>-1595.44813550641</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2627471.749</t>
+          <t>1500.77654164002</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2156338.612</t>
+          <t>5.75199453630395</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1675195.417</t>
+          <t>4735.61227113594</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2778749.986</t>
+          <t>-3631258298.69334</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2458663.898</t>
+          <t>-40274442663.4523</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2574704.106</t>
+          <t>-63834946360.2229</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2917386.068</t>
+          <t>-123454091870.529</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3193301.745</t>
+          <t>-169672141928.431</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3681081.128</t>
+          <t>-208157678943.511</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4143364.003</t>
+          <t>-238809424112.065</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4630949.826</t>
+          <t>-274525581809.402</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>5392239.48</t>
+          <t>-384206952128.885</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5331722.704</t>
+          <t>-353179806193.626</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>5164430.122</t>
+          <t>-309592899627.359</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>4547536.921</t>
+          <t>-298168287029.987</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>4008345.454</t>
+          <t>-164819031079.251</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3032180.262</t>
+          <t>-217713191404.844</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2269275.883</t>
+          <t>-125722422889.028</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>19987.24093</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>19839.50688</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>21004.95335</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>21506.88258</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>21052.34763</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>20218.01639</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>22287.38455</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>27489.32314</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>34425.34388</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>42627.21957</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>45109.00249</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>46021.06443</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>55049.77476</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>61036.95136</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>48116.3818</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1222523.554</t>
+          <t>-0.0410738683150281</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1069467.716</t>
+          <t>-0.0344291908447112</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1113812.458</t>
+          <t>-0.0242670939838284</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1246961.935</t>
+          <t>-0.0172324492165466</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1326941.97</t>
+          <t>-0.0124614418703762</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1537968.039</t>
+          <t>-0.010252537138698</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1774625.546</t>
+          <t>0.00741037300038007</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2111383.37</t>
+          <t>0.0159835358501152</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2521402.883</t>
+          <t>0.0148345130957084</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2544544.379</t>
+          <t>0.0198230264854926</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2456827.299</t>
+          <t>0.0214324277259212</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2090343.914</t>
+          <t>0.0297520079050075</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1870355.62</t>
+          <t>0.0308227694530658</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1540236.802</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1200156.809</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>21148.7209385179</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>20803.7284565732</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>20896.892847196</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>21375.3848137194</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>21042.4432893277</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>20903.7686172109</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>23865.8383132277</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>30331.645055342</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>38730.082244585</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>46963.7342737843</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>51508.7043663024</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>52097.0567684416</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>63835.9978007698</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>71859.7339886758</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>58694.778280572</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>379458.373</t>
+          <t>24971.7648136563</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>334891.352</t>
+          <t>24752.0798094449</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>345330.766</t>
+          <t>24891.6820905812</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>392164.266</t>
+          <t>25207.9121430708</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>411009.23</t>
+          <t>24783.9985822109</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>462268.534</t>
+          <t>25389.3433363619</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>563765.664</t>
+          <t>27584.067228164</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>689566.246</t>
+          <t>34873.9763075699</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>835698.627</t>
+          <t>44286.4464960014</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>837424.294</t>
+          <t>53622.4462388657</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>816872.419</t>
+          <t>58247.945903252</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>707151.14</t>
+          <t>58545.1124246822</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>648678.5</t>
+          <t>71423.5215695397</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>545942.373</t>
+          <t>80623.5198120911</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>433244.136</t>
+          <t>65872.4146455416</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>254508.305141285</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>249505.11536862</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>236307.741572287</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>218297.248732917</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>215051.488527582</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>194374.693144571</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>201827.141007188</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>239499.926519695</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>286938.955093062</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>339376.053194343</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>361040.650152018</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>364782.048612521</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>430985.282906479</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1087.098</t>
+          <t>24971.7648136563</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>946.847</t>
+          <t>24775.7840494616</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>964.118</t>
+          <t>25302.4336942737</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1044.722</t>
+          <t>26190.3434797752</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1119.654</t>
+          <t>27318.1584757885</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1275.961</t>
+          <t>31058.6095478455</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1308.962</t>
+          <t>31658.271507544</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1249.679</t>
+          <t>32527.6414934527</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1180.469</t>
+          <t>33952.2146604049</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>967.297</t>
+          <t>35971.814201749</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>863.648</t>
+          <t>37808.9184917026</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>708.379</t>
+          <t>38345.4618063611</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>520.184</t>
+          <t>39236.0631869847</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>343.563</t>
+          <t>40047.6064220182</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>331.94</t>
+          <t>36328.8278319403</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21148.7209385179</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>20822.9393252611</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>21187.0643231323</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>22186.2279949465</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>23072.8170770861</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>25635.8940397122</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>27194.2887541933</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>28131.6448231774</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>29536.4599401748</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>30943.8943744316</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>32789.0455548352</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>33583.7260163434</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>35055.1848610708</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>35097.9564721635</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>31443.9014030932</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>13850.9408063437</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>15060.9085605551</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>15990.5193994188</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>16886.8671869292</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>17372.8220977891</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>15207.2777736381</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>18526.120611836</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>23180.8819824301</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>27667.0362439986</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>34110.5884811343</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>36254.152226748</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>39114.7730953178</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>46772.7932904603</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>53384.4235179089</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>43149.8243844584</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1700913671240.09</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1456604195524.18</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1463262594119.15</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1652763835509.8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1786710485337.57</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1970168214604.26</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2338071076183.82</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2900406618495.95</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>3613602567473.04</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3516110732275.34</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3453061074854.67</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2929416483861.01</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2627471748832.43</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2156338611804.47</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1675195417273.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2034609715237.83</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1827089295517.74</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1931779595577.48</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2206594251127.53</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2359332904026.24</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2797644450712.7</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3266956618929.02</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3981909587458.89</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>4831895180801.91</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>4921050108578.29</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>4791441489054.26</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>4154325102615.51</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3814945215610.9</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3230660555311.95</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2584947355624.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1222523553579.55</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1069467715675.26</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1113812457565.59</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1246961935227.82</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1326941970485.29</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1537968039251.1</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1774625545981.35</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2111383369949.8</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2521402883393.69</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2544544378613.58</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2456827299428.9</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2090343914027.86</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1870355620174.92</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1540236802002.95</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1200156809070.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4025461</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4030099</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4026318</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4096782</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4208414</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4250367</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4231638</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4223693</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4226739</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4166006</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4155867</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4181597</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4169042</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4068691.46704218</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>3957946.60261327</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3333796</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3298792</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3304041</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3401781</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3478082</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3562351</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3589329</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3598020</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3647173</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3599362</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3627317</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3673501</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3682953</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3646566</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3560689</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>8079711219.40055</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8069551307.42483</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>8160661798.29138</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>8290864349.17157</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>8587374640.12717</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8673528917</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8452564657</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8474813414</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>8369326785</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>8304771954</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>8284194674</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>8317391408</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>8277404373</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>8076163693.74774</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7854806818.35529</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6653528427.29386</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6558125225.49215</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6659476570.14462</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6856272880.13977</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>7066930465.10046</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6961416731.94834</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7127011526.85595</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7176955593.93508</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>7159213271.18566</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7123600011.05471</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7199948537.14686</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7275750066.84333</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>7282680540.18446</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7217871138.19669</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6982465348.42156</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.248673669020027</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.248673669020027</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.248673669020027</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.248673669020027</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.274666085932445</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.264220981115569</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.260565849336195</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.260562595586571</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.232534470264458</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.29407658987496</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.301025358744711</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.306541028936287</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.307605667431767</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.32737349179284</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.331122973069948</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.613892332189813</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.613892332189813</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.613892332189813</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.613892332189813</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.615653264914631</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.606726649721676</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.611500965395145</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.615664483182112</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.582153996933471</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.596512468348034</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.592116281423768</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.594573862935085</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.593801367594568</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.579629299768395</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.585373655534772</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.13743399879016</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.13743399879016</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.13743399879016</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.13743399879016</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.109680649152924</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.129052369162755</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.127933185268661</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.123772921231317</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.185311532802071</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.109410941777007</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.106858359831521</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0988851081286282</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0985929649736658</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0929972084387651</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.08350337139528</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.130850879536823</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.130850879536823</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.130850879536823</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.130850879536823</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.144064009987499</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.136418385920244</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.137101331933868</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.138390127093662</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.145542680314531</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.160630703934852</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.165916046885304</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.16998333704836</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.170997793877179</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.184809619463623</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.18737099784991</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.677970253379368</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.677970253379368</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.677970253379368</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.677970253379368</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.697700742937093</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.681231637034883</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.683591719541622</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.689952099210062</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.690699698721832</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.682681886601219</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.679949049644513</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.686344318430707</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.68926932743156</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.675402957988325</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.685755771781092</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.191178867083809</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.191178867083809</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.191178867083809</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.191178867083809</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.158235247075407</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.182349977044873</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.17930694852451</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.171657773696276</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.163757620963638</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.156687409463929</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.154134903470183</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.143672344520933</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.13973287869126</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.139787422548052</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.126873230368998</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>91385.57973</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>94429.68677</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>97266.8189</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>101699.33222</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>104654.9122</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>104478.0818</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>115643.71912</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>138588.23325</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>172524.36307</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>208623.28951</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>228843.61944</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>242887.26422</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>293236.43547</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>335691.56586</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>264522.8033</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>38822.70562</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>39812.98837</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>40882.20149</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>42094.77933</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>42156.82068</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>40596.62111</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>46110.18784</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>58054.85829</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>71953.48274</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>87733.03472</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>94502.09813</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>97659.88552</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>118196.31486</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>134007.94333</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>109022.23903</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>31813537.022513</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>31357857.2603804</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>31103651.2424806</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>31134426.1538356</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>31302815.7833249</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>31668203.8084991</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>32157092.0553171</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>32756186.3130027</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>33389246.8345595</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>34196828.6281147</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>35181113.6314742</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>36082293.3732993</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>37043834.6988152</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
